--- a/Report Files/DeliveryReceipt/DeliveryReceiptExcel.xlsx
+++ b/Report Files/DeliveryReceipt/DeliveryReceiptExcel.xlsx
@@ -49,8 +49,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -331,9 +334,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="D1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+  </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Report Files/DeliveryReceipt/DeliveryReceiptExcel.xlsx
+++ b/Report Files/DeliveryReceipt/DeliveryReceiptExcel.xlsx
@@ -52,7 +52,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -334,36 +334,182 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="D1:H3"/>
+  <dimension ref="B6:C47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="55.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-  </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Report Files/DeliveryReceipt/DeliveryReceiptExcel.xlsx
+++ b/Report Files/DeliveryReceipt/DeliveryReceiptExcel.xlsx
@@ -338,7 +338,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="55.42578125" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">

--- a/Report Files/DeliveryReceipt/DeliveryReceiptExcel.xlsx
+++ b/Report Files/DeliveryReceipt/DeliveryReceiptExcel.xlsx
@@ -334,54 +334,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B6:C47"/>
+  <dimension ref="B1:D47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="55.42578125" customWidth="1"/>
+    <col min="4" max="4" width="55.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D1"/>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D2"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
